--- a/testData/TestLoginData.xlsx
+++ b/testData/TestLoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lokesh\eclipse-workspace\OpencartV121\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D78C38F-E237-4EDA-B614-FD913671500C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512D24F0-EC21-4A6C-850E-4BA2B42E30ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F056C827-F4D0-4017-A7C3-4017245BEDA5}"/>
   </bookViews>
@@ -514,7 +514,7 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
